--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/90.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/90.xlsx
@@ -426,13 +426,13 @@
         <v>-5.606990620604659</v>
       </c>
       <c r="E2">
-        <v>-1.456903528965501</v>
+        <v>-4.057083777044282</v>
       </c>
       <c r="F2">
-        <v>-1.20680802638337</v>
+        <v>-1.688545089481423</v>
       </c>
       <c r="G2">
-        <v>-9.90468666825455</v>
+        <v>-10.32500871519002</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.209298052740015</v>
       </c>
       <c r="E3">
-        <v>-2.463126955899661</v>
+        <v>-4.571243032635405</v>
       </c>
       <c r="F3">
-        <v>-1.558914702984731</v>
+        <v>-1.663849800469164</v>
       </c>
       <c r="G3">
-        <v>-10.24915614183981</v>
+        <v>-9.774402680924224</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.697333186501989</v>
       </c>
       <c r="E4">
-        <v>-4.822242359051418</v>
+        <v>-5.861853451825874</v>
       </c>
       <c r="F4">
-        <v>-1.914174974288549</v>
+        <v>-1.807735561600633</v>
       </c>
       <c r="G4">
-        <v>-9.040916598795537</v>
+        <v>-9.157276179849161</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.118804385675693</v>
       </c>
       <c r="E5">
-        <v>-5.457268370617703</v>
+        <v>-6.356986846337959</v>
       </c>
       <c r="F5">
-        <v>-1.282411462502075</v>
+        <v>-1.818731310505393</v>
       </c>
       <c r="G5">
-        <v>-8.952798747356281</v>
+        <v>-9.134134539793532</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.455654294289732</v>
       </c>
       <c r="E6">
-        <v>-6.093120871237628</v>
+        <v>-7.359576213362894</v>
       </c>
       <c r="F6">
-        <v>-1.333374281857107</v>
+        <v>-1.898257894643757</v>
       </c>
       <c r="G6">
-        <v>-8.356798391512507</v>
+        <v>-8.407115272017034</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.714935860755037</v>
       </c>
       <c r="E7">
-        <v>-7.028012893667857</v>
+        <v>-8.159414109932349</v>
       </c>
       <c r="F7">
-        <v>-1.156908830773534</v>
+        <v>-1.670691286848885</v>
       </c>
       <c r="G7">
-        <v>-8.214920087453047</v>
+        <v>-7.711918370061614</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.894091334779757</v>
       </c>
       <c r="E8">
-        <v>-8.538402949745603</v>
+        <v>-9.411831597779695</v>
       </c>
       <c r="F8">
-        <v>-1.303120647572063</v>
+        <v>-1.888736639715979</v>
       </c>
       <c r="G8">
-        <v>-7.364840762629832</v>
+        <v>-7.105815738022527</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.997250982657618</v>
       </c>
       <c r="E9">
-        <v>-8.69713868658055</v>
+        <v>-10.07439340042959</v>
       </c>
       <c r="F9">
-        <v>-1.057087245266582</v>
+        <v>-1.796407637367349</v>
       </c>
       <c r="G9">
-        <v>-6.720958045612744</v>
+        <v>-6.026074433008259</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.03508507320793897</v>
       </c>
       <c r="E10">
-        <v>-11.58720893192104</v>
+        <v>-11.51541652096005</v>
       </c>
       <c r="F10">
-        <v>-0.7408563325130652</v>
+        <v>-2.062406350815104</v>
       </c>
       <c r="G10">
-        <v>-5.595716683864554</v>
+        <v>-5.41679974629097</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.9674271119829213</v>
       </c>
       <c r="E11">
-        <v>-10.09750186824094</v>
+        <v>-12.36984007397173</v>
       </c>
       <c r="F11">
-        <v>-0.7379313672137802</v>
+        <v>-1.935309940203576</v>
       </c>
       <c r="G11">
-        <v>-4.409509214424686</v>
+        <v>-5.274848341382958</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.976512426063544</v>
       </c>
       <c r="E12">
-        <v>-11.78360598904953</v>
+        <v>-12.96786512584512</v>
       </c>
       <c r="F12">
-        <v>-1.115213785921023</v>
+        <v>-2.277943407186521</v>
       </c>
       <c r="G12">
-        <v>-4.489147367432006</v>
+        <v>-4.055755933073427</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.952538999214994</v>
       </c>
       <c r="E13">
-        <v>-12.62013750767385</v>
+        <v>-14.33032194774379</v>
       </c>
       <c r="F13">
-        <v>-1.100201283480088</v>
+        <v>-2.111158257572063</v>
       </c>
       <c r="G13">
-        <v>-4.132725905108629</v>
+        <v>-3.296010981847323</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.849459086457215</v>
       </c>
       <c r="E14">
-        <v>-14.41409222016559</v>
+        <v>-15.6333504687955</v>
       </c>
       <c r="F14">
-        <v>-1.078220554446803</v>
+        <v>-2.133589618472471</v>
       </c>
       <c r="G14">
-        <v>-3.524657382392433</v>
+        <v>-2.148244115767007</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.629336527554174</v>
       </c>
       <c r="E15">
-        <v>-14.25352907034771</v>
+        <v>-17.09065417771929</v>
       </c>
       <c r="F15">
-        <v>-0.4716526655838791</v>
+        <v>-2.220141586553977</v>
       </c>
       <c r="G15">
-        <v>-2.581087293761452</v>
+        <v>-1.82535766771648</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.274699250811029</v>
       </c>
       <c r="E16">
-        <v>-15.54715472096001</v>
+        <v>-17.77229998640677</v>
       </c>
       <c r="F16">
-        <v>-0.4073448473697479</v>
+        <v>-2.091120878465746</v>
       </c>
       <c r="G16">
-        <v>-1.113535544204852</v>
+        <v>-1.175976722590508</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.791185394299331</v>
       </c>
       <c r="E17">
-        <v>-16.43329219564808</v>
+        <v>-18.76593502981538</v>
       </c>
       <c r="F17">
-        <v>-0.5042083328813024</v>
+        <v>-1.599731678390274</v>
       </c>
       <c r="G17">
-        <v>-1.05141026591472</v>
+        <v>-0.4280271154270541</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.200543471204149</v>
       </c>
       <c r="E18">
-        <v>-17.40918056706569</v>
+        <v>-19.38950648454778</v>
       </c>
       <c r="F18">
-        <v>-0.5308519420249457</v>
+        <v>-1.791089518641376</v>
       </c>
       <c r="G18">
-        <v>-0.6836398968537736</v>
+        <v>-0.07848496510126067</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.532720338282173</v>
       </c>
       <c r="E19">
-        <v>-18.8484219599378</v>
+        <v>-20.5523931958658</v>
       </c>
       <c r="F19">
-        <v>-0.4272530011612284</v>
+        <v>-1.68550829458276</v>
       </c>
       <c r="G19">
-        <v>-0.7061915086318102</v>
+        <v>-0.08632764185296499</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.818231897605137</v>
       </c>
       <c r="E20">
-        <v>-20.31179766381848</v>
+        <v>-21.35199851260106</v>
       </c>
       <c r="F20">
-        <v>-0.1884073428098385</v>
+        <v>-1.392354040936432</v>
       </c>
       <c r="G20">
-        <v>0.4971946602175833</v>
+        <v>0.7254938317320757</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>7.072850820700655</v>
       </c>
       <c r="E21">
-        <v>-20.64226453572376</v>
+        <v>-22.41316477215138</v>
       </c>
       <c r="F21">
-        <v>0.9956982992849008</v>
+        <v>-1.265832517302446</v>
       </c>
       <c r="G21">
-        <v>0.0329494462812277</v>
+        <v>1.031721118546709</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>7.298172745143934</v>
       </c>
       <c r="E22">
-        <v>-20.82994400228144</v>
+        <v>-23.14638515907059</v>
       </c>
       <c r="F22">
-        <v>0.590579422373983</v>
+        <v>-0.9304886834641364</v>
       </c>
       <c r="G22">
-        <v>0.9405748033817615</v>
+        <v>0.5690580158325675</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>7.48401979828022</v>
       </c>
       <c r="E23">
-        <v>-20.71312662734799</v>
+        <v>-23.36547120966662</v>
       </c>
       <c r="F23">
-        <v>0.3181136446125724</v>
+        <v>-0.8054855572794827</v>
       </c>
       <c r="G23">
-        <v>0.4426118230511778</v>
+        <v>0.6581079030908507</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.61502248498331</v>
       </c>
       <c r="E24">
-        <v>-22.8154988128215</v>
+        <v>-24.21682969272057</v>
       </c>
       <c r="F24">
-        <v>0.7657551054113972</v>
+        <v>-0.534515811047528</v>
       </c>
       <c r="G24">
-        <v>0.06294690163311935</v>
+        <v>0.1739531509026651</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.671744338466545</v>
       </c>
       <c r="E25">
-        <v>-22.09688942334304</v>
+        <v>-24.45957243502282</v>
       </c>
       <c r="F25">
-        <v>0.6813891989058788</v>
+        <v>-0.7381989298848843</v>
       </c>
       <c r="G25">
-        <v>-0.558673996255545</v>
+        <v>0.4070247635297126</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>7.638470497748871</v>
       </c>
       <c r="E26">
-        <v>-22.43312925898983</v>
+        <v>-24.47012989821054</v>
       </c>
       <c r="F26">
-        <v>0.8522581998161384</v>
+        <v>-0.6000479562829968</v>
       </c>
       <c r="G26">
-        <v>-0.07551654850116486</v>
+        <v>0.05821623243402208</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>7.508410173738053</v>
       </c>
       <c r="E27">
-        <v>-22.26607048665993</v>
+        <v>-24.37967295555577</v>
       </c>
       <c r="F27">
-        <v>0.501443776363145</v>
+        <v>-0.4691750186821058</v>
       </c>
       <c r="G27">
-        <v>0.1624710961909489</v>
+        <v>-0.5179881525476356</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>7.284796898608422</v>
       </c>
       <c r="E28">
-        <v>-21.69931080963985</v>
+        <v>-24.53321717823468</v>
       </c>
       <c r="F28">
-        <v>0.5124022487347797</v>
+        <v>-0.3364440529967354</v>
       </c>
       <c r="G28">
-        <v>-0.07447747215390178</v>
+        <v>-0.9095763445133085</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.986144196267191</v>
       </c>
       <c r="E29">
-        <v>-21.55422667842962</v>
+        <v>-24.44067532349485</v>
       </c>
       <c r="F29">
-        <v>0.732512721537053</v>
+        <v>-0.3979420489805707</v>
       </c>
       <c r="G29">
-        <v>0.05910649633959171</v>
+        <v>-0.9006136583320166</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.639709965681726</v>
       </c>
       <c r="E30">
-        <v>-22.06601860356559</v>
+        <v>-23.60867911163725</v>
       </c>
       <c r="F30">
-        <v>0.59097206852291</v>
+        <v>-0.4895619688324044</v>
       </c>
       <c r="G30">
-        <v>-0.5124350988023377</v>
+        <v>-1.137034856269462</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.27933048315967</v>
       </c>
       <c r="E31">
-        <v>-21.12046528766452</v>
+        <v>-24.50681106063142</v>
       </c>
       <c r="F31">
-        <v>0.4101949651077654</v>
+        <v>-0.3395380052461915</v>
       </c>
       <c r="G31">
-        <v>-0.6105860417052417</v>
+        <v>-1.162481783799044</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.938175791003594</v>
       </c>
       <c r="E32">
-        <v>-21.72572108045444</v>
+        <v>-23.66894636117184</v>
       </c>
       <c r="F32">
-        <v>0.884829606094215</v>
+        <v>-0.5042696320691096</v>
       </c>
       <c r="G32">
-        <v>-1.194479069507728</v>
+        <v>-1.386661200348759</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.649203543777568</v>
       </c>
       <c r="E33">
-        <v>-20.94401610452918</v>
+        <v>-23.19391450947192</v>
       </c>
       <c r="F33">
-        <v>1.021145745898902</v>
+        <v>-0.5579428695661007</v>
       </c>
       <c r="G33">
-        <v>-1.250048768129574</v>
+        <v>-1.367297307716472</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.436543913677333</v>
       </c>
       <c r="E34">
-        <v>-19.78755025791935</v>
+        <v>-23.63195370790159</v>
       </c>
       <c r="F34">
-        <v>0.1036783168868784</v>
+        <v>-0.339048440111137</v>
       </c>
       <c r="G34">
-        <v>-1.602405301124588</v>
+        <v>-1.262136515586429</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.315601184452822</v>
       </c>
       <c r="E35">
-        <v>-19.86327991321627</v>
+        <v>-22.54799877781194</v>
       </c>
       <c r="F35">
-        <v>0.6440604786335247</v>
+        <v>-0.110193721004912</v>
       </c>
       <c r="G35">
-        <v>-1.531458316861084</v>
+        <v>-1.098032942822821</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.288442324310871</v>
       </c>
       <c r="E36">
-        <v>-19.42994630321764</v>
+        <v>-21.57636329479095</v>
       </c>
       <c r="F36">
-        <v>0.8420444297396205</v>
+        <v>-0.1897832610658885</v>
       </c>
       <c r="G36">
-        <v>-1.058994478951904</v>
+        <v>-1.793937356562432</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.344848323276492</v>
       </c>
       <c r="E37">
-        <v>-18.01184475598891</v>
+        <v>-21.3009015536717</v>
       </c>
       <c r="F37">
-        <v>1.134204642502589</v>
+        <v>-0.3575790189117619</v>
       </c>
       <c r="G37">
-        <v>-1.181054620820223</v>
+        <v>-1.818629778905181</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.46167857322933</v>
       </c>
       <c r="E38">
-        <v>-18.66166450629423</v>
+        <v>-21.24144833355678</v>
       </c>
       <c r="F38">
-        <v>0.7531225025187047</v>
+        <v>-0.211992619502346</v>
       </c>
       <c r="G38">
-        <v>-1.151934375650946</v>
+        <v>-1.47359638448824</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.608141093340138</v>
       </c>
       <c r="E39">
-        <v>-17.87483031438282</v>
+        <v>-20.49997551573514</v>
       </c>
       <c r="F39">
-        <v>0.408606156429196</v>
+        <v>-0.1507572159851982</v>
       </c>
       <c r="G39">
-        <v>-1.307816713697138</v>
+        <v>-1.218704168568668</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.752111758141395</v>
       </c>
       <c r="E40">
-        <v>-16.43368259751261</v>
+        <v>-19.54123160066642</v>
       </c>
       <c r="F40">
-        <v>1.029154401949167</v>
+        <v>-0.05769096664807652</v>
       </c>
       <c r="G40">
-        <v>-1.552822039850164</v>
+        <v>-1.569562134168383</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.860745794045809</v>
       </c>
       <c r="E41">
-        <v>-14.94577387433616</v>
+        <v>-18.15792981112843</v>
       </c>
       <c r="F41">
-        <v>0.9376612223099619</v>
+        <v>-0.1325149090407475</v>
       </c>
       <c r="G41">
-        <v>-1.383807656510672</v>
+        <v>-1.305093707088607</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.902805267714205</v>
       </c>
       <c r="E42">
-        <v>-16.11721620098333</v>
+        <v>-17.80701252665969</v>
       </c>
       <c r="F42">
-        <v>1.135510149529401</v>
+        <v>0.002863518863970139</v>
       </c>
       <c r="G42">
-        <v>-1.359049965553145</v>
+        <v>-1.314544602508437</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.852203666381468</v>
       </c>
       <c r="E43">
-        <v>-15.48327833078415</v>
+        <v>-17.7558449631378</v>
       </c>
       <c r="F43">
-        <v>1.284859822049735</v>
+        <v>-0.1509477404878421</v>
       </c>
       <c r="G43">
-        <v>-2.051988573437251</v>
+        <v>-1.391906186232306</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.697668574568832</v>
       </c>
       <c r="E44">
-        <v>-14.70596329922924</v>
+        <v>-15.98298856417619</v>
       </c>
       <c r="F44">
-        <v>0.8851858040774188</v>
+        <v>0.04849827908419491</v>
       </c>
       <c r="G44">
-        <v>-1.599392501866443</v>
+        <v>-1.80662035378606</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.439650013239916</v>
       </c>
       <c r="E45">
-        <v>-13.43352733279622</v>
+        <v>-16.05107215742411</v>
       </c>
       <c r="F45">
-        <v>0.8890327422960197</v>
+        <v>0.1969963899144511</v>
       </c>
       <c r="G45">
-        <v>-2.19789786714539</v>
+        <v>-2.1316476124013</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.092133469901435</v>
       </c>
       <c r="E46">
-        <v>-13.1667374969232</v>
+        <v>-15.46815233513912</v>
       </c>
       <c r="F46">
-        <v>0.8733086722560794</v>
+        <v>-0.07990943712596486</v>
       </c>
       <c r="G46">
-        <v>-2.469566727807457</v>
+        <v>-1.899207799965302</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.679300427565067</v>
       </c>
       <c r="E47">
-        <v>-12.27430790707802</v>
+        <v>-13.92371840583175</v>
       </c>
       <c r="F47">
-        <v>0.8988985980633618</v>
+        <v>-0.1496090987649181</v>
       </c>
       <c r="G47">
-        <v>-2.71114153556776</v>
+        <v>-2.673732176321698</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.233397618378551</v>
       </c>
       <c r="E48">
-        <v>-11.20036636949253</v>
+        <v>-12.98614340888569</v>
       </c>
       <c r="F48">
-        <v>1.070311007989858</v>
+        <v>-0.001303169172111374</v>
       </c>
       <c r="G48">
-        <v>-2.62174703002345</v>
+        <v>-2.78731000901349</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.784442409716077</v>
       </c>
       <c r="E49">
-        <v>-10.8286913348223</v>
+        <v>-13.02835664879124</v>
       </c>
       <c r="F49">
-        <v>1.126595259540473</v>
+        <v>-0.2351811082089126</v>
       </c>
       <c r="G49">
-        <v>-2.417025492911302</v>
+        <v>-2.930459745688823</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>3.355262893533989</v>
       </c>
       <c r="E50">
-        <v>-9.181905665625862</v>
+        <v>-11.9503574237414</v>
       </c>
       <c r="F50">
-        <v>0.8957590856067517</v>
+        <v>-0.03978332013435681</v>
       </c>
       <c r="G50">
-        <v>-3.05542303554246</v>
+        <v>-3.346429681390903</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.961314812327452</v>
       </c>
       <c r="E51">
-        <v>-9.43254781586794</v>
+        <v>-11.23967651468203</v>
       </c>
       <c r="F51">
-        <v>0.6259556806779387</v>
+        <v>-0.001945982276683791</v>
       </c>
       <c r="G51">
-        <v>-3.23758773938739</v>
+        <v>-3.442494639365507</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.61147282211764</v>
       </c>
       <c r="E52">
-        <v>-8.580516512579365</v>
+        <v>-10.14471557458159</v>
       </c>
       <c r="F52">
-        <v>0.8105913194553233</v>
+        <v>-0.157104167025448</v>
       </c>
       <c r="G52">
-        <v>-4.174322898678836</v>
+        <v>-3.560207891489623</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.306732623379749</v>
       </c>
       <c r="E53">
-        <v>-9.209366698905628</v>
+        <v>-10.29271941335318</v>
       </c>
       <c r="F53">
-        <v>1.018317699585744</v>
+        <v>0.1180504913254498</v>
       </c>
       <c r="G53">
-        <v>-3.924299721421691</v>
+        <v>-3.514809653794754</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.040446021453653</v>
       </c>
       <c r="E54">
-        <v>-7.400788529339168</v>
+        <v>-8.166428883859984</v>
       </c>
       <c r="F54">
-        <v>1.14043065190203</v>
+        <v>-0.06172760100191851</v>
       </c>
       <c r="G54">
-        <v>-3.566768692647091</v>
+        <v>-4.017949740649516</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.804155941871896</v>
       </c>
       <c r="E55">
-        <v>-6.53016745216066</v>
+        <v>-8.78787389439408</v>
       </c>
       <c r="F55">
-        <v>1.044727709121798</v>
+        <v>-0.1034856017770416</v>
       </c>
       <c r="G55">
-        <v>-3.579780643689199</v>
+        <v>-4.565394163215469</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.58655071125049</v>
       </c>
       <c r="E56">
-        <v>-5.478914908042709</v>
+        <v>-7.213387327940255</v>
       </c>
       <c r="F56">
-        <v>0.6046840341414501</v>
+        <v>-0.04669853121292708</v>
       </c>
       <c r="G56">
-        <v>-4.474263512518069</v>
+        <v>-4.68642567171489</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.376527366622067</v>
       </c>
       <c r="E57">
-        <v>-6.326140945828458</v>
+        <v>-6.891903852130576</v>
       </c>
       <c r="F57">
-        <v>0.8437276723021091</v>
+        <v>-0.01203218377317057</v>
       </c>
       <c r="G57">
-        <v>-4.750307981114841</v>
+        <v>-4.616264521573312</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.165044005438594</v>
       </c>
       <c r="E58">
-        <v>-5.069387505357991</v>
+        <v>-6.582605898347945</v>
       </c>
       <c r="F58">
-        <v>0.9130040381982317</v>
+        <v>0.09552801001073404</v>
       </c>
       <c r="G58">
-        <v>-5.248605136753087</v>
+        <v>-5.20790101783304</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.9499038860661406</v>
       </c>
       <c r="E59">
-        <v>-3.549013129255357</v>
+        <v>-6.29508323154139</v>
       </c>
       <c r="F59">
-        <v>0.8726509485382566</v>
+        <v>-0.02215151996576933</v>
       </c>
       <c r="G59">
-        <v>-4.990885484441339</v>
+        <v>-5.529771886237624</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.7307158880346486</v>
       </c>
       <c r="E60">
-        <v>-3.959852946718721</v>
+        <v>-5.342805866505428</v>
       </c>
       <c r="F60">
-        <v>0.9227307282419035</v>
+        <v>-0.06625214375600941</v>
       </c>
       <c r="G60">
-        <v>-4.889990648973175</v>
+        <v>-5.53663292302307</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.5066971818961901</v>
       </c>
       <c r="E61">
-        <v>-4.515195445806844</v>
+        <v>-4.946149265716353</v>
       </c>
       <c r="F61">
-        <v>1.102214750141278</v>
+        <v>-0.2972059458609284</v>
       </c>
       <c r="G61">
-        <v>-5.329196211536163</v>
+        <v>-5.602434129697489</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.2763950264179387</v>
       </c>
       <c r="E62">
-        <v>-3.564865936882227</v>
+        <v>-4.360338808349288</v>
       </c>
       <c r="F62">
-        <v>1.173460973721258</v>
+        <v>-0.3997594870623128</v>
       </c>
       <c r="G62">
-        <v>-4.950784447521839</v>
+        <v>-5.706937014190571</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.04021328056044284</v>
       </c>
       <c r="E63">
-        <v>-2.781624272766787</v>
+        <v>-3.329370548341799</v>
       </c>
       <c r="F63">
-        <v>0.8691138197283027</v>
+        <v>-0.2128151883333259</v>
       </c>
       <c r="G63">
-        <v>-5.068944136971036</v>
+        <v>-6.104412435209205</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.199646679499092</v>
       </c>
       <c r="E64">
-        <v>-2.712427618883819</v>
+        <v>-3.969696057558564</v>
       </c>
       <c r="F64">
-        <v>0.5774274331197352</v>
+        <v>-0.2528601253194596</v>
       </c>
       <c r="G64">
-        <v>-5.351993233305764</v>
+        <v>-6.409514491105067</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.4430700707667884</v>
       </c>
       <c r="E65">
-        <v>-2.419987549868666</v>
+        <v>-3.059548868201663</v>
       </c>
       <c r="F65">
-        <v>0.4079757688356656</v>
+        <v>-0.1768590728474106</v>
       </c>
       <c r="G65">
-        <v>-6.783482767825316</v>
+        <v>-6.264623387787462</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.6904423380828941</v>
       </c>
       <c r="E66">
-        <v>-2.371112558998084</v>
+        <v>-3.438608312607439</v>
       </c>
       <c r="F66">
-        <v>0.4977161230505472</v>
+        <v>-0.3150746591067165</v>
       </c>
       <c r="G66">
-        <v>-6.299745734771709</v>
+        <v>-6.49495110784925</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.942850819315172</v>
       </c>
       <c r="E67">
-        <v>-1.380002668074976</v>
+        <v>-3.479741717568541</v>
       </c>
       <c r="F67">
-        <v>0.908908589758791</v>
+        <v>-0.4160617575494071</v>
       </c>
       <c r="G67">
-        <v>-5.671845996141418</v>
+        <v>-6.068901087280882</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.200109548148293</v>
       </c>
       <c r="E68">
-        <v>-2.903994491241535</v>
+        <v>-2.633973456957807</v>
       </c>
       <c r="F68">
-        <v>0.7397625930463544</v>
+        <v>-0.4523508767312478</v>
       </c>
       <c r="G68">
-        <v>-5.48159581629781</v>
+        <v>-6.705544209546812</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.462764872131949</v>
       </c>
       <c r="E69">
-        <v>-2.246183962347242</v>
+        <v>-3.398384460926475</v>
       </c>
       <c r="F69">
-        <v>0.3748361025192685</v>
+        <v>-0.5211542448403719</v>
       </c>
       <c r="G69">
-        <v>-6.547124227758058</v>
+        <v>-6.241627949428937</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.729228465625126</v>
       </c>
       <c r="E70">
-        <v>-1.803613610362187</v>
+        <v>-2.992491118150982</v>
       </c>
       <c r="F70">
-        <v>0.2767259240665007</v>
+        <v>-0.2070000491656734</v>
       </c>
       <c r="G70">
-        <v>-6.27001196462352</v>
+        <v>-6.037373735598598</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.996464273864007</v>
       </c>
       <c r="E71">
-        <v>-1.328399017363981</v>
+        <v>-3.159267472110797</v>
       </c>
       <c r="F71">
-        <v>0.7016394684347155</v>
+        <v>-0.4987427647576313</v>
       </c>
       <c r="G71">
-        <v>-5.988542368766415</v>
+        <v>-6.203558071801322</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.260093948802712</v>
       </c>
       <c r="E72">
-        <v>-2.528099793865278</v>
+        <v>-2.814953793648536</v>
       </c>
       <c r="F72">
-        <v>0.2005865342381841</v>
+        <v>-0.3807708210879397</v>
       </c>
       <c r="G72">
-        <v>-5.28655492012951</v>
+        <v>-6.116622887661841</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.514322175043074</v>
       </c>
       <c r="E73">
-        <v>-1.242348631924858</v>
+        <v>-2.665903345623089</v>
       </c>
       <c r="F73">
-        <v>0.4884292960977619</v>
+        <v>-0.443194103460702</v>
       </c>
       <c r="G73">
-        <v>-6.294996790360474</v>
+        <v>-6.294720051433816</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.752527579606183</v>
       </c>
       <c r="E74">
-        <v>-3.001441288555987</v>
+        <v>-2.710870164637008</v>
       </c>
       <c r="F74">
-        <v>0.03648032480437968</v>
+        <v>-0.547823533373502</v>
       </c>
       <c r="G74">
-        <v>-6.096131153366193</v>
+        <v>-6.032470757256487</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.967756289598812</v>
       </c>
       <c r="E75">
-        <v>-3.661590075426159</v>
+        <v>-3.047508708570986</v>
       </c>
       <c r="F75">
-        <v>0.2284983738755135</v>
+        <v>-0.4142931931444301</v>
       </c>
       <c r="G75">
-        <v>-5.575227560313497</v>
+        <v>-5.66610757953015</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.154496526695673</v>
       </c>
       <c r="E76">
-        <v>-4.78163641192857</v>
+        <v>-3.951355476348121</v>
       </c>
       <c r="F76">
-        <v>-0.4017964425057968</v>
+        <v>-0.7071301820754862</v>
       </c>
       <c r="G76">
-        <v>-5.038672553437077</v>
+        <v>-5.401571273091005</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.308618294694139</v>
       </c>
       <c r="E77">
-        <v>-2.785773330880291</v>
+        <v>-4.115959700785051</v>
       </c>
       <c r="F77">
-        <v>0.2589135398041029</v>
+        <v>-0.3195983734934046</v>
       </c>
       <c r="G77">
-        <v>-4.707235916850654</v>
+        <v>-5.144394655654209</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.429023847009133</v>
       </c>
       <c r="E78">
-        <v>-3.737589689459197</v>
+        <v>-4.150846675913611</v>
       </c>
       <c r="F78">
-        <v>-0.1799497116272556</v>
+        <v>-0.8276692363264534</v>
       </c>
       <c r="G78">
-        <v>-4.883254927928103</v>
+        <v>-5.041233693880959</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.515655480668426</v>
       </c>
       <c r="E79">
-        <v>-6.279238730337169</v>
+        <v>-4.539691086200683</v>
       </c>
       <c r="F79">
-        <v>-0.3014770081897626</v>
+        <v>-0.6234725296993613</v>
       </c>
       <c r="G79">
-        <v>-4.725344041334615</v>
+        <v>-4.678478565179542</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.569653925608272</v>
       </c>
       <c r="E80">
-        <v>-5.006661554719105</v>
+        <v>-5.737543683662432</v>
       </c>
       <c r="F80">
-        <v>0.220183221886212</v>
+        <v>-0.5774343545539732</v>
       </c>
       <c r="G80">
-        <v>-4.726607641716715</v>
+        <v>-4.567161637303653</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.591115431974107</v>
       </c>
       <c r="E81">
-        <v>-6.820697043966391</v>
+        <v>-6.611121847304218</v>
       </c>
       <c r="F81">
-        <v>-0.4374460620526763</v>
+        <v>-0.4287059575857387</v>
       </c>
       <c r="G81">
-        <v>-4.061559618299472</v>
+        <v>-4.034781211028423</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.581563919297666</v>
       </c>
       <c r="E82">
-        <v>-6.61540796139144</v>
+        <v>-6.912466401399803</v>
       </c>
       <c r="F82">
-        <v>-0.1476276439374216</v>
+        <v>-0.7390629170860042</v>
       </c>
       <c r="G82">
-        <v>-3.821874989623134</v>
+        <v>-3.982910937492184</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.544608504614736</v>
       </c>
       <c r="E83">
-        <v>-7.915246816145679</v>
+        <v>-7.085061404425701</v>
       </c>
       <c r="F83">
-        <v>-0.1038360011884258</v>
+        <v>-0.5413415584465958</v>
       </c>
       <c r="G83">
-        <v>-3.914830550789723</v>
+        <v>-3.953709759240582</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.486631797900785</v>
       </c>
       <c r="E84">
-        <v>-7.915620605164913</v>
+        <v>-8.797683779543323</v>
       </c>
       <c r="F84">
-        <v>-0.1245493280954274</v>
+        <v>-0.9024211107550808</v>
       </c>
       <c r="G84">
-        <v>-3.12889460982557</v>
+        <v>-3.607796543896436</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.415844039933491</v>
       </c>
       <c r="E85">
-        <v>-9.970147796176397</v>
+        <v>-9.463310652150945</v>
       </c>
       <c r="F85">
-        <v>0.2616852571338701</v>
+        <v>-0.6971268173192793</v>
       </c>
       <c r="G85">
-        <v>-3.081068379660966</v>
+        <v>-3.021120462359823</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.341241978369715</v>
       </c>
       <c r="E86">
-        <v>-9.831430537927123</v>
+        <v>-10.73424315608438</v>
       </c>
       <c r="F86">
-        <v>-0.3579865756739393</v>
+        <v>-0.4202400427291277</v>
       </c>
       <c r="G86">
-        <v>-3.052741800847387</v>
+        <v>-2.910059387453864</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.274175724192339</v>
       </c>
       <c r="E87">
-        <v>-12.24249846154116</v>
+        <v>-12.01053745583816</v>
       </c>
       <c r="F87">
-        <v>-0.1737584936587321</v>
+        <v>-0.8419519470855225</v>
       </c>
       <c r="G87">
-        <v>-2.732748057803814</v>
+        <v>-2.933088765492074</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.228617743953782</v>
       </c>
       <c r="E88">
-        <v>-14.95868620834505</v>
+        <v>-13.40226195794291</v>
       </c>
       <c r="F88">
-        <v>-0.2323803980200475</v>
+        <v>-1.051125485068634</v>
       </c>
       <c r="G88">
-        <v>-2.674123788010365</v>
+        <v>-2.68140515467498</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.222171941026852</v>
       </c>
       <c r="E89">
-        <v>-15.48282563074974</v>
+        <v>-15.51136234576264</v>
       </c>
       <c r="F89">
-        <v>-0.4805311074070842</v>
+        <v>-1.053483847064404</v>
       </c>
       <c r="G89">
-        <v>-2.443208650415577</v>
+        <v>-2.835903798087882</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.269932772193445</v>
       </c>
       <c r="E90">
-        <v>-17.61642165896331</v>
+        <v>-16.96171357892866</v>
       </c>
       <c r="F90">
-        <v>-0.1479241994676239</v>
+        <v>-0.962361776021653</v>
       </c>
       <c r="G90">
-        <v>-2.375822721774352</v>
+        <v>-2.600722703831215</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.385647503967379</v>
       </c>
       <c r="E91">
-        <v>-18.06815814834226</v>
+        <v>-18.28905499907592</v>
       </c>
       <c r="F91">
-        <v>0.2184428219729303</v>
+        <v>-0.9715815052148115</v>
       </c>
       <c r="G91">
-        <v>-2.383900365539256</v>
+        <v>-2.865055372192253</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.575668769004291</v>
       </c>
       <c r="E92">
-        <v>-21.13360189508496</v>
+        <v>-20.0340225839913</v>
       </c>
       <c r="F92">
-        <v>0.2345794189794647</v>
+        <v>-1.093435178534022</v>
       </c>
       <c r="G92">
-        <v>-2.642554664414623</v>
+        <v>-2.865000546555839</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.839347182784656</v>
       </c>
       <c r="E93">
-        <v>-22.36375817023122</v>
+        <v>-22.03553818565267</v>
       </c>
       <c r="F93">
-        <v>-0.09151320770438033</v>
+        <v>-0.9683972609184502</v>
       </c>
       <c r="G93">
-        <v>-2.245191505413408</v>
+        <v>-2.884474090460953</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.166445923780896</v>
       </c>
       <c r="E94">
-        <v>-24.50212208504569</v>
+        <v>-24.45671917884267</v>
       </c>
       <c r="F94">
-        <v>0.3764182842586156</v>
+        <v>-0.9702329230830539</v>
       </c>
       <c r="G94">
-        <v>-3.052710471912293</v>
+        <v>-2.647880583380494</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.543233325451036</v>
       </c>
       <c r="E95">
-        <v>-26.88344470915131</v>
+        <v>-26.89912308190254</v>
       </c>
       <c r="F95">
-        <v>-0.05719063273678562</v>
+        <v>-1.022965135210465</v>
       </c>
       <c r="G95">
-        <v>-2.584071374829094</v>
+        <v>-3.1197491715229</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.949115266023298</v>
       </c>
       <c r="E96">
-        <v>-29.86361887418395</v>
+        <v>-28.85237213815241</v>
       </c>
       <c r="F96">
-        <v>-0.3578532085220886</v>
+        <v>-0.988481856966727</v>
       </c>
       <c r="G96">
-        <v>-2.427210007561235</v>
+        <v>-3.411110878635734</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.357810571469465</v>
       </c>
       <c r="E97">
-        <v>-30.459529941493</v>
+        <v>-31.94449819105147</v>
       </c>
       <c r="F97">
-        <v>-0.5990207807035255</v>
+        <v>-0.9831678800777682</v>
       </c>
       <c r="G97">
-        <v>-2.967545372605587</v>
+        <v>-4.140456319842915</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.746539685225117</v>
       </c>
       <c r="E98">
-        <v>-35.46736832668814</v>
+        <v>-34.25143887693507</v>
       </c>
       <c r="F98">
-        <v>-0.6699646501814835</v>
+        <v>-1.293454428348796</v>
       </c>
       <c r="G98">
-        <v>-2.832112996941585</v>
+        <v>-3.852971568447884</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.091564766580639</v>
       </c>
       <c r="E99">
-        <v>-38.31194429517645</v>
+        <v>-36.44406865091975</v>
       </c>
       <c r="F99">
-        <v>-0.254936842398278</v>
+        <v>-1.093735047533835</v>
       </c>
       <c r="G99">
-        <v>-3.87817047524131</v>
+        <v>-3.742017534070161</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.383791643187346</v>
       </c>
       <c r="E100">
-        <v>-40.11259606092948</v>
+        <v>-39.30988621872891</v>
       </c>
       <c r="F100">
-        <v>-0.4989664239563872</v>
+        <v>-1.23103611618045</v>
       </c>
       <c r="G100">
-        <v>-3.203736825019015</v>
+        <v>-3.904492002208914</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.606299499649215</v>
       </c>
       <c r="E101">
-        <v>-42.03899875917566</v>
+        <v>-41.46028613996273</v>
       </c>
       <c r="F101">
-        <v>-0.6323907331579007</v>
+        <v>-1.207697692973977</v>
       </c>
       <c r="G101">
-        <v>-3.985827139200457</v>
+        <v>-4.187501937374777</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.774369829693254</v>
       </c>
       <c r="E102">
-        <v>-44.65018086405392</v>
+        <v>-43.96118802453281</v>
       </c>
       <c r="F102">
-        <v>-0.5937879838200409</v>
+        <v>-1.254190641823502</v>
       </c>
       <c r="G102">
-        <v>-3.793135913164159</v>
+        <v>-4.23396535886282</v>
       </c>
     </row>
   </sheetData>
